--- a/data/dividends_info_20260713.xlsx
+++ b/data/dividends_info_20260713.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61.5099983215332</v>
+        <v>61.56000137329102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1463176759159382</v>
+        <v>0.1461988271479283</v>
       </c>
       <c r="J2" t="n">
         <v>245</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.69999694824219</v>
+        <v>65.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.065449060144482</v>
+        <v>1.068702290076336</v>
       </c>
       <c r="J3" t="n">
         <v>224</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.899999618530273</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6060606294135134</v>
+        <v>0.6134969492659876</v>
       </c>
       <c r="J4" t="n">
         <v>154</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J5" t="n">
         <v>154</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.5099983215332</v>
+        <v>61.56000137329102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1463176759159382</v>
+        <v>0.1461988271479283</v>
       </c>
       <c r="J6" t="n">
         <v>154</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.18499946594238</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="I8" t="n">
-        <v>1.274486697222059</v>
+        <v>1.252319140482866</v>
       </c>
       <c r="J8" t="n">
         <v>133</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.039999961853027</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I9" t="n">
-        <v>3.311258299058689</v>
+        <v>3.300330064166073</v>
       </c>
       <c r="J9" t="n">
         <v>126</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.800000190734863</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8823529164271378</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="J10" t="n">
         <v>98</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I11" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J11" t="n">
         <v>98</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.889999866485596</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7770961357369177</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J13" t="n">
         <v>77</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.18499946594238</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="I14" t="n">
-        <v>1.274486697222059</v>
+        <v>1.252319140482866</v>
       </c>
       <c r="J14" t="n">
         <v>70</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61.5099983215332</v>
+        <v>61.56000137329102</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1463176759159382</v>
+        <v>0.1461988271479283</v>
       </c>
       <c r="J15" t="n">
         <v>70</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I17" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J17" t="n">
         <v>42</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.889999866485596</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7770961357369177</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J18" t="n">
         <v>21</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.820000171661377</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I19" t="n">
-        <v>4.295532519351027</v>
+        <v>4.317789320329981</v>
       </c>
       <c r="J19" t="n">
         <v>14</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.179999828338623</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I20" t="n">
-        <v>3.349282434196755</v>
+        <v>3.286384799954511</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.17199993133545</v>
+        <v>10.2180004119873</v>
       </c>
       <c r="I21" t="n">
-        <v>2.55603619499696</v>
+        <v>2.544529159491709</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.65999984741211</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="I22" t="n">
-        <v>4.092769483254234</v>
+        <v>4.126547466122097</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.838000059127808</v>
+        <v>2.822000026702881</v>
       </c>
       <c r="I23" t="n">
-        <v>7.75193782298975</v>
+        <v>7.795889366345604</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4620000123977661</v>
       </c>
       <c r="I24" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8658008425671074</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.860000133514404</v>
+        <v>6.864999771118164</v>
       </c>
       <c r="I25" t="n">
-        <v>3.498542205961257</v>
+        <v>3.495994289900887</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.89999961853027</v>
+        <v>19</v>
       </c>
       <c r="I26" t="n">
-        <v>1.989418029571574</v>
+        <v>1.978947368421053</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.699999809265137</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="I28" t="n">
-        <v>2.105263228341595</v>
+        <v>2.101576168096538</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.220000028610229</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="I30" t="n">
-        <v>4.658385051777184</v>
+        <v>4.777069904097268</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.200000047683716</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I31" t="n">
-        <v>3.863636279894303</v>
+        <v>3.828828779484834</v>
       </c>
       <c r="J31" t="n">
         <v>-7</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.659999847412109</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>1.502145971933323</v>
+        <v>1.446280946139471</v>
       </c>
       <c r="J32" t="n">
         <v>-7</v>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>36.54999923706055</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4103967253928277</v>
+        <v>0.4120878948132904</v>
       </c>
       <c r="J33" t="n">
         <v>-7</v>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9.649999618530273</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I34" t="n">
-        <v>23.13886101831865</v>
+        <v>23.25937407575551</v>
       </c>
       <c r="J34" t="n">
         <v>-7</v>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.25</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7766990147433418</v>
       </c>
       <c r="J35" t="n">
         <v>-14</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.42000007629395</v>
+        <v>21.52000045776367</v>
       </c>
       <c r="I36" t="n">
-        <v>1.16713351591759</v>
+        <v>1.161710012463353</v>
       </c>
       <c r="J36" t="n">
         <v>-21</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.914999961853027</v>
+        <v>1.865000009536743</v>
       </c>
       <c r="I38" t="n">
-        <v>1.723237632238276</v>
+        <v>1.769436988270957</v>
       </c>
       <c r="J38" t="n">
         <v>-21</v>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.164999961853027</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I39" t="n">
-        <v>5.614714465476158</v>
+        <v>5.642023492858249</v>
       </c>
       <c r="J39" t="n">
         <v>-21</v>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.808000087738037</v>
+        <v>3.832000017166138</v>
       </c>
       <c r="I40" t="n">
-        <v>4.201680575460292</v>
+        <v>4.175365325763336</v>
       </c>
       <c r="J40" t="n">
         <v>-21</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.539999961853027</v>
+        <v>2.552000045776367</v>
       </c>
       <c r="I41" t="n">
-        <v>5.456692995337133</v>
+        <v>5.431034385339724</v>
       </c>
       <c r="J41" t="n">
         <v>-21</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>51.2599983215332</v>
+        <v>51.15000152587891</v>
       </c>
       <c r="I42" t="n">
-        <v>1.229028522490901</v>
+        <v>1.231671517509646</v>
       </c>
       <c r="J42" t="n">
         <v>-21</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.244999885559082</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="I43" t="n">
-        <v>2.241793475829128</v>
+        <v>2.272727329024459</v>
       </c>
       <c r="J43" t="n">
         <v>-21</v>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
       <c r="I44" t="n">
-        <v>4.656716417910448</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>-21</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>28.72999954223633</v>
+        <v>28.71999931335449</v>
       </c>
       <c r="I45" t="n">
-        <v>2.958579928796742</v>
+        <v>2.95961009861431</v>
       </c>
       <c r="J45" t="n">
         <v>-21</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>61.5099983215332</v>
+        <v>61.56000137329102</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1463176759159382</v>
+        <v>0.1461988271479283</v>
       </c>
       <c r="J46" t="n">
         <v>-21</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.490000009536743</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6711409353016787</v>
+        <v>0.6578947450975963</v>
       </c>
       <c r="J47" t="n">
         <v>-21</v>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.789999961853027</v>
+        <v>9.670000076293945</v>
       </c>
       <c r="I49" t="n">
-        <v>2.655771205445315</v>
+        <v>2.688728003605619</v>
       </c>
       <c r="J49" t="n">
         <v>-21</v>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10.22999954223633</v>
+        <v>10.25500011444092</v>
       </c>
       <c r="I50" t="n">
-        <v>2.707722506304692</v>
+        <v>2.701121374049848</v>
       </c>
       <c r="J50" t="n">
         <v>-21</v>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.134999990463257</v>
+        <v>1.154999971389771</v>
       </c>
       <c r="I51" t="n">
-        <v>1.189427322769395</v>
+        <v>1.168831197784008</v>
       </c>
       <c r="J51" t="n">
         <v>-28</v>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.610000014305115</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="I53" t="n">
-        <v>1.490683216568699</v>
+        <v>1.481481477120831</v>
       </c>
       <c r="J53" t="n">
         <v>-28</v>
@@ -3893,7 +3893,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3920,14 +3920,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3937,14 +3937,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3971,14 +3971,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3988,14 +3988,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4192,14 +4192,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4209,14 +4209,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4379,14 +4379,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4420,7 +4420,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4532,14 +4532,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4590,7 +4590,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4634,14 +4634,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4770,14 +4770,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4787,14 +4787,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4821,14 +4821,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4855,14 +4855,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4923,14 +4923,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4974,14 +4974,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5008,14 +5008,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5059,14 +5059,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5127,14 +5127,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5229,14 +5229,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5280,14 +5280,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5314,14 +5314,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5348,14 +5348,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5365,14 +5365,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5382,14 +5382,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5416,14 +5416,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5450,14 +5450,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5518,14 +5518,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5552,14 +5552,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5593,7 +5593,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5610,7 +5610,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5678,7 +5678,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5705,14 +5705,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5780,7 +5780,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5824,14 +5824,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5865,7 +5865,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5882,7 +5882,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5892,14 +5892,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6001,7 +6001,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6018,7 +6018,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6103,7 +6103,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6113,14 +6113,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6137,7 +6137,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6147,14 +6147,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6198,14 +6198,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6215,14 +6215,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6239,7 +6239,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6273,7 +6273,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6317,14 +6317,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6334,14 +6334,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6375,7 +6375,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6409,7 +6409,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6426,7 +6426,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6436,14 +6436,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6460,7 +6460,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6470,14 +6470,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6487,14 +6487,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6511,7 +6511,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6623,14 +6623,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6640,14 +6640,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6657,14 +6657,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6674,14 +6674,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6691,14 +6691,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6715,7 +6715,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6759,14 +6759,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6804,44 +6804,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>